--- a/data/merged/processed/monitoring_sites.xlsx
+++ b/data/merged/processed/monitoring_sites.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/wc_biotoxin_depuration/data/merged/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81EDA04-B5A2-3745-8368-1EC3BAB6BABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6911C77B-585B-7D45-9C48-ED128AC9459B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11160" yWindow="2080" windowWidth="28040" windowHeight="17440" xr2:uid="{11D15602-BF62-9841-8597-0CE8ABA34C41}"/>
   </bookViews>
